--- a/quarantine_hotel_instances/penality_study.xlsx
+++ b/quarantine_hotel_instances/penality_study.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,7 +11,17 @@
     <sheet name="3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sheet1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -1217,7 +1227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1256,13 +1266,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>217</v>
+        <v>781</v>
       </c>
       <c r="C2" s="1">
-        <v>664</v>
+        <v>743</v>
       </c>
       <c r="D2" s="1">
-        <v>259</v>
+        <v>119</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -1283,13 +1293,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>907</v>
+        <v>987</v>
       </c>
       <c r="C3" s="1">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="D3" s="1">
-        <v>369</v>
+        <v>747</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1310,13 +1320,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>540</v>
+        <v>907</v>
       </c>
       <c r="C4" s="1">
-        <v>307</v>
+        <v>777</v>
       </c>
       <c r="D4" s="1">
-        <v>120</v>
+        <v>892</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1401,46 +1411,46 @@
         <v>1</v>
       </c>
       <c r="B7" s="1">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="D7" s="1">
-        <v>226</v>
+        <v>310</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1">
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>294</v>
+        <v>175</v>
       </c>
       <c r="M7" s="1">
-        <v>336</v>
+        <v>540</v>
       </c>
       <c r="N7" s="1">
-        <v>998</v>
+        <v>971</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1">
         <v>1</v>
       </c>
       <c r="Q7" s="1">
-        <v>169936</v>
+        <v>204168</v>
       </c>
     </row>
     <row r="8">
@@ -1448,23 +1458,23 @@
         <v>2</v>
       </c>
       <c r="B8" s="1">
-        <v>217</v>
+        <v>109</v>
       </c>
       <c r="C8" s="1">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="D8" s="1">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1">
         <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
@@ -1474,20 +1484,20 @@
         <v>2</v>
       </c>
       <c r="L8" s="1">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="M8" s="1">
-        <v>419</v>
+        <v>542</v>
       </c>
       <c r="N8" s="1">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
         <v>2</v>
       </c>
       <c r="Q8" s="1">
-        <v>60076</v>
+        <v>149448</v>
       </c>
     </row>
     <row r="9">
@@ -1495,46 +1505,46 @@
         <v>3</v>
       </c>
       <c r="B9" s="1">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="C9" s="1">
-        <v>115</v>
+        <v>318</v>
       </c>
       <c r="D9" s="1">
-        <v>242</v>
+        <v>322</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1">
         <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H9" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I9" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
         <v>3</v>
       </c>
       <c r="L9" s="1">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="M9" s="1">
-        <v>339</v>
+        <v>448</v>
       </c>
       <c r="N9" s="1">
-        <v>933</v>
+        <v>732</v>
       </c>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
         <v>3</v>
       </c>
       <c r="Q9" s="1">
-        <v>138189</v>
+        <v>214478</v>
       </c>
     </row>
     <row r="10">
@@ -1542,46 +1552,46 @@
         <v>4</v>
       </c>
       <c r="B10" s="1">
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="C10" s="1">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="D10" s="1">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H10" s="1">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I10" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
         <v>4</v>
       </c>
       <c r="L10" s="1">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="M10" s="1">
-        <v>599</v>
+        <v>491</v>
       </c>
       <c r="N10" s="1">
-        <v>859</v>
+        <v>737</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1">
         <v>4</v>
       </c>
       <c r="Q10" s="1">
-        <v>97862</v>
+        <v>151920</v>
       </c>
     </row>
     <row r="11">
@@ -1589,46 +1599,46 @@
         <v>5</v>
       </c>
       <c r="B11" s="1">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="C11" s="1">
-        <v>235</v>
+        <v>313</v>
       </c>
       <c r="D11" s="1">
-        <v>314</v>
+        <v>10</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1">
         <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I11" s="1">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
         <v>5</v>
       </c>
       <c r="L11" s="1">
-        <v>277</v>
+        <v>186</v>
       </c>
       <c r="M11" s="1">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="N11" s="1">
-        <v>627</v>
+        <v>767</v>
       </c>
       <c r="O11" s="1"/>
       <c r="P11" s="1">
         <v>5</v>
       </c>
       <c r="Q11" s="1">
-        <v>208593</v>
+        <v>118842</v>
       </c>
     </row>
     <row r="12">
@@ -1636,46 +1646,46 @@
         <v>6</v>
       </c>
       <c r="B12" s="1">
-        <v>313</v>
+        <v>94</v>
       </c>
       <c r="C12" s="1">
-        <v>361</v>
+        <v>228</v>
       </c>
       <c r="D12" s="1">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1">
         <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H12" s="1">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I12" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
         <v>6</v>
       </c>
       <c r="L12" s="1">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="M12" s="1">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="N12" s="1">
-        <v>582</v>
+        <v>521</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1">
         <v>6</v>
       </c>
       <c r="Q12" s="1">
-        <v>161622</v>
+        <v>65708</v>
       </c>
     </row>
     <row r="13">
@@ -1683,46 +1693,46 @@
         <v>7</v>
       </c>
       <c r="B13" s="1">
-        <v>339</v>
+        <v>274</v>
       </c>
       <c r="C13" s="1">
-        <v>83</v>
+        <v>358</v>
       </c>
       <c r="D13" s="1">
-        <v>275</v>
+        <v>183</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1">
         <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
         <v>7</v>
       </c>
       <c r="L13" s="1">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="M13" s="1">
-        <v>529</v>
+        <v>389</v>
       </c>
       <c r="N13" s="1">
-        <v>725</v>
+        <v>631</v>
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1">
         <v>7</v>
       </c>
       <c r="Q13" s="1">
-        <v>141981</v>
+        <v>145314</v>
       </c>
     </row>
     <row r="14">
@@ -1730,46 +1740,46 @@
         <v>8</v>
       </c>
       <c r="B14" s="1">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C14" s="1">
-        <v>362</v>
+        <v>216</v>
       </c>
       <c r="D14" s="1">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1">
         <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H14" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I14" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
         <v>8</v>
       </c>
       <c r="L14" s="1">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="M14" s="1">
-        <v>540</v>
+        <v>388</v>
       </c>
       <c r="N14" s="1">
-        <v>587</v>
+        <v>534</v>
       </c>
       <c r="O14" s="1"/>
       <c r="P14" s="1">
         <v>8</v>
       </c>
       <c r="Q14" s="1">
-        <v>150798</v>
+        <v>91023</v>
       </c>
     </row>
     <row r="15">
@@ -1777,46 +1787,46 @@
         <v>9</v>
       </c>
       <c r="B15" s="1">
-        <v>159</v>
+        <v>372</v>
       </c>
       <c r="C15" s="1">
-        <v>5</v>
+        <v>268</v>
       </c>
       <c r="D15" s="1">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1">
         <v>9</v>
       </c>
       <c r="G15" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
         <v>9</v>
       </c>
       <c r="L15" s="1">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="M15" s="1">
-        <v>411</v>
+        <v>308</v>
       </c>
       <c r="N15" s="1">
-        <v>723</v>
+        <v>609</v>
       </c>
       <c r="O15" s="1"/>
       <c r="P15" s="1">
         <v>9</v>
       </c>
       <c r="Q15" s="1">
-        <v>102082</v>
+        <v>135334</v>
       </c>
     </row>
     <row r="16">
@@ -1824,46 +1834,46 @@
         <v>10</v>
       </c>
       <c r="B16" s="1">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C16" s="1">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D16" s="1">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1">
         <v>10</v>
       </c>
       <c r="G16" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" s="1">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
         <v>10</v>
       </c>
       <c r="L16" s="1">
-        <v>208</v>
+        <v>298</v>
       </c>
       <c r="M16" s="1">
-        <v>365</v>
+        <v>588</v>
       </c>
       <c r="N16" s="1">
-        <v>778</v>
+        <v>585</v>
       </c>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
         <v>10</v>
       </c>
       <c r="Q16" s="1">
-        <v>58130</v>
+        <v>73013</v>
       </c>
     </row>
     <row r="17">
@@ -1871,46 +1881,46 @@
         <v>11</v>
       </c>
       <c r="B17" s="1">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C17" s="1">
-        <v>355</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1">
-        <v>205</v>
+        <v>346</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1">
         <v>11</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I17" s="1">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
         <v>11</v>
       </c>
       <c r="L17" s="1">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="M17" s="1">
-        <v>559</v>
+        <v>463</v>
       </c>
       <c r="N17" s="1">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="O17" s="1"/>
       <c r="P17" s="1">
         <v>11</v>
       </c>
       <c r="Q17" s="1">
-        <v>197188</v>
+        <v>142296</v>
       </c>
     </row>
     <row r="18">
@@ -1918,46 +1928,46 @@
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>353</v>
+        <v>255</v>
       </c>
       <c r="C18" s="1">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="D18" s="1">
-        <v>349</v>
+        <v>268</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1">
         <v>12</v>
       </c>
       <c r="G18" s="1">
+        <v>19</v>
+      </c>
+      <c r="H18" s="1">
         <v>6</v>
       </c>
-      <c r="H18" s="1">
-        <v>1</v>
-      </c>
       <c r="I18" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
         <v>12</v>
       </c>
       <c r="L18" s="1">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="M18" s="1">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="N18" s="1">
-        <v>982</v>
+        <v>521</v>
       </c>
       <c r="O18" s="1"/>
       <c r="P18" s="1">
         <v>12</v>
       </c>
       <c r="Q18" s="1">
-        <v>269250</v>
+        <v>168571</v>
       </c>
     </row>
     <row r="19">
@@ -1981,6 +1991,4763 @@
     </row>
     <row r="20">
       <c r="A20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>570</v>
+      </c>
+      <c r="C2" s="1">
+        <v>246</v>
+      </c>
+      <c r="D2" s="1">
+        <v>537</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>530</v>
+      </c>
+      <c r="C3" s="1">
+        <v>912</v>
+      </c>
+      <c r="D3" s="1">
+        <v>433</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>768</v>
+      </c>
+      <c r="C4" s="1">
+        <v>281</v>
+      </c>
+      <c r="D4" s="1">
+        <v>602</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1">
+        <v>155</v>
+      </c>
+      <c r="D7" s="1">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>176</v>
+      </c>
+      <c r="M7" s="1">
+        <v>431</v>
+      </c>
+      <c r="N7" s="1">
+        <v>540</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>64772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1">
+        <v>148</v>
+      </c>
+      <c r="D8" s="1">
+        <v>359</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>124</v>
+      </c>
+      <c r="M8" s="1">
+        <v>490</v>
+      </c>
+      <c r="N8" s="1">
+        <v>978</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>215903</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>213</v>
+      </c>
+      <c r="C9" s="1">
+        <v>94</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>173</v>
+      </c>
+      <c r="M9" s="1">
+        <v>460</v>
+      </c>
+      <c r="N9" s="1">
+        <v>733</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>41510</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>280</v>
+      </c>
+      <c r="C10" s="1">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1">
+        <v>261</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>277</v>
+      </c>
+      <c r="M10" s="1">
+        <v>537</v>
+      </c>
+      <c r="N10" s="1">
+        <v>563</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>122454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>224</v>
+      </c>
+      <c r="C11" s="1">
+        <v>191</v>
+      </c>
+      <c r="D11" s="1">
+        <v>170</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>246</v>
+      </c>
+      <c r="M11" s="1">
+        <v>555</v>
+      </c>
+      <c r="N11" s="1">
+        <v>510</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>123904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>356</v>
+      </c>
+      <c r="C12" s="1">
+        <v>204</v>
+      </c>
+      <c r="D12" s="1">
+        <v>174</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>157</v>
+      </c>
+      <c r="M12" s="1">
+        <v>345</v>
+      </c>
+      <c r="N12" s="1">
+        <v>790</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>131866</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>268</v>
+      </c>
+      <c r="C13" s="1">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1">
+        <v>323</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>18</v>
+      </c>
+      <c r="H13" s="1">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1">
+        <v>19</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>128</v>
+      </c>
+      <c r="M13" s="1">
+        <v>545</v>
+      </c>
+      <c r="N13" s="1">
+        <v>682</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>147732</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1">
+        <v>139</v>
+      </c>
+      <c r="D14" s="1">
+        <v>321</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>215</v>
+      </c>
+      <c r="M14" s="1">
+        <v>490</v>
+      </c>
+      <c r="N14" s="1">
+        <v>574</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>126612</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>132</v>
+      </c>
+      <c r="C15" s="1">
+        <v>219</v>
+      </c>
+      <c r="D15" s="1">
+        <v>268</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>259</v>
+      </c>
+      <c r="M15" s="1">
+        <v>412</v>
+      </c>
+      <c r="N15" s="1">
+        <v>504</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>129744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>251</v>
+      </c>
+      <c r="C16" s="1">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1">
+        <v>132</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1">
+        <v>15</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>122</v>
+      </c>
+      <c r="M16" s="1">
+        <v>334</v>
+      </c>
+      <c r="N16" s="1">
+        <v>918</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>80575</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1">
+        <v>295</v>
+      </c>
+      <c r="D17" s="1">
+        <v>42</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>140</v>
+      </c>
+      <c r="M17" s="1">
+        <v>373</v>
+      </c>
+      <c r="N17" s="1">
+        <v>511</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>67988</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>155</v>
+      </c>
+      <c r="C18" s="1">
+        <v>285</v>
+      </c>
+      <c r="D18" s="1">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>18</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>174</v>
+      </c>
+      <c r="M18" s="1">
+        <v>544</v>
+      </c>
+      <c r="N18" s="1">
+        <v>571</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>102140</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>200</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>570</v>
+      </c>
+      <c r="C2" s="1">
+        <v>246</v>
+      </c>
+      <c r="D2" s="1">
+        <v>537</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>530</v>
+      </c>
+      <c r="C3" s="1">
+        <v>912</v>
+      </c>
+      <c r="D3" s="1">
+        <v>433</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>768</v>
+      </c>
+      <c r="C4" s="1">
+        <v>281</v>
+      </c>
+      <c r="D4" s="1">
+        <v>602</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1">
+        <v>155</v>
+      </c>
+      <c r="D7" s="1">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>176</v>
+      </c>
+      <c r="M7" s="1">
+        <v>431</v>
+      </c>
+      <c r="N7" s="1">
+        <v>540</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>64772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1">
+        <v>148</v>
+      </c>
+      <c r="D8" s="1">
+        <v>359</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>124</v>
+      </c>
+      <c r="M8" s="1">
+        <v>490</v>
+      </c>
+      <c r="N8" s="1">
+        <v>978</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>215903</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>213</v>
+      </c>
+      <c r="C9" s="1">
+        <v>94</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>173</v>
+      </c>
+      <c r="M9" s="1">
+        <v>460</v>
+      </c>
+      <c r="N9" s="1">
+        <v>733</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>41510</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>280</v>
+      </c>
+      <c r="C10" s="1">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1">
+        <v>261</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>277</v>
+      </c>
+      <c r="M10" s="1">
+        <v>537</v>
+      </c>
+      <c r="N10" s="1">
+        <v>563</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>122454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>224</v>
+      </c>
+      <c r="C11" s="1">
+        <v>191</v>
+      </c>
+      <c r="D11" s="1">
+        <v>170</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>246</v>
+      </c>
+      <c r="M11" s="1">
+        <v>555</v>
+      </c>
+      <c r="N11" s="1">
+        <v>510</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>123904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>356</v>
+      </c>
+      <c r="C12" s="1">
+        <v>204</v>
+      </c>
+      <c r="D12" s="1">
+        <v>174</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>157</v>
+      </c>
+      <c r="M12" s="1">
+        <v>345</v>
+      </c>
+      <c r="N12" s="1">
+        <v>790</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>131866</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>268</v>
+      </c>
+      <c r="C13" s="1">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1">
+        <v>323</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>18</v>
+      </c>
+      <c r="H13" s="1">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1">
+        <v>19</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>128</v>
+      </c>
+      <c r="M13" s="1">
+        <v>545</v>
+      </c>
+      <c r="N13" s="1">
+        <v>682</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>147732</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1">
+        <v>139</v>
+      </c>
+      <c r="D14" s="1">
+        <v>321</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>215</v>
+      </c>
+      <c r="M14" s="1">
+        <v>490</v>
+      </c>
+      <c r="N14" s="1">
+        <v>574</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>126612</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>132</v>
+      </c>
+      <c r="C15" s="1">
+        <v>219</v>
+      </c>
+      <c r="D15" s="1">
+        <v>268</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>259</v>
+      </c>
+      <c r="M15" s="1">
+        <v>412</v>
+      </c>
+      <c r="N15" s="1">
+        <v>504</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>129744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>251</v>
+      </c>
+      <c r="C16" s="1">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1">
+        <v>132</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1">
+        <v>15</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>122</v>
+      </c>
+      <c r="M16" s="1">
+        <v>334</v>
+      </c>
+      <c r="N16" s="1">
+        <v>918</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>80575</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1">
+        <v>295</v>
+      </c>
+      <c r="D17" s="1">
+        <v>42</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>140</v>
+      </c>
+      <c r="M17" s="1">
+        <v>373</v>
+      </c>
+      <c r="N17" s="1">
+        <v>511</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>67988</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>155</v>
+      </c>
+      <c r="C18" s="1">
+        <v>285</v>
+      </c>
+      <c r="D18" s="1">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>18</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>174</v>
+      </c>
+      <c r="M18" s="1">
+        <v>544</v>
+      </c>
+      <c r="N18" s="1">
+        <v>571</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>102140</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>400</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>570</v>
+      </c>
+      <c r="C2" s="1">
+        <v>246</v>
+      </c>
+      <c r="D2" s="1">
+        <v>537</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>530</v>
+      </c>
+      <c r="C3" s="1">
+        <v>912</v>
+      </c>
+      <c r="D3" s="1">
+        <v>433</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>768</v>
+      </c>
+      <c r="C4" s="1">
+        <v>281</v>
+      </c>
+      <c r="D4" s="1">
+        <v>602</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1">
+        <v>155</v>
+      </c>
+      <c r="D7" s="1">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>176</v>
+      </c>
+      <c r="M7" s="1">
+        <v>431</v>
+      </c>
+      <c r="N7" s="1">
+        <v>540</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>64772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1">
+        <v>148</v>
+      </c>
+      <c r="D8" s="1">
+        <v>359</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>124</v>
+      </c>
+      <c r="M8" s="1">
+        <v>490</v>
+      </c>
+      <c r="N8" s="1">
+        <v>978</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>215903</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>213</v>
+      </c>
+      <c r="C9" s="1">
+        <v>94</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>173</v>
+      </c>
+      <c r="M9" s="1">
+        <v>460</v>
+      </c>
+      <c r="N9" s="1">
+        <v>733</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>41510</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>280</v>
+      </c>
+      <c r="C10" s="1">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1">
+        <v>261</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>277</v>
+      </c>
+      <c r="M10" s="1">
+        <v>537</v>
+      </c>
+      <c r="N10" s="1">
+        <v>563</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>122454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>224</v>
+      </c>
+      <c r="C11" s="1">
+        <v>191</v>
+      </c>
+      <c r="D11" s="1">
+        <v>170</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>246</v>
+      </c>
+      <c r="M11" s="1">
+        <v>555</v>
+      </c>
+      <c r="N11" s="1">
+        <v>510</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>123904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>356</v>
+      </c>
+      <c r="C12" s="1">
+        <v>204</v>
+      </c>
+      <c r="D12" s="1">
+        <v>174</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>157</v>
+      </c>
+      <c r="M12" s="1">
+        <v>345</v>
+      </c>
+      <c r="N12" s="1">
+        <v>790</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>131866</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>268</v>
+      </c>
+      <c r="C13" s="1">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1">
+        <v>323</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>18</v>
+      </c>
+      <c r="H13" s="1">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1">
+        <v>19</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>128</v>
+      </c>
+      <c r="M13" s="1">
+        <v>545</v>
+      </c>
+      <c r="N13" s="1">
+        <v>682</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>147732</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1">
+        <v>139</v>
+      </c>
+      <c r="D14" s="1">
+        <v>321</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>215</v>
+      </c>
+      <c r="M14" s="1">
+        <v>490</v>
+      </c>
+      <c r="N14" s="1">
+        <v>574</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>126612</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>132</v>
+      </c>
+      <c r="C15" s="1">
+        <v>219</v>
+      </c>
+      <c r="D15" s="1">
+        <v>268</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>259</v>
+      </c>
+      <c r="M15" s="1">
+        <v>412</v>
+      </c>
+      <c r="N15" s="1">
+        <v>504</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>129744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>251</v>
+      </c>
+      <c r="C16" s="1">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1">
+        <v>132</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1">
+        <v>15</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>122</v>
+      </c>
+      <c r="M16" s="1">
+        <v>334</v>
+      </c>
+      <c r="N16" s="1">
+        <v>918</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>80575</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1">
+        <v>295</v>
+      </c>
+      <c r="D17" s="1">
+        <v>42</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>140</v>
+      </c>
+      <c r="M17" s="1">
+        <v>373</v>
+      </c>
+      <c r="N17" s="1">
+        <v>511</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>67988</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>155</v>
+      </c>
+      <c r="C18" s="1">
+        <v>285</v>
+      </c>
+      <c r="D18" s="1">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>18</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>174</v>
+      </c>
+      <c r="M18" s="1">
+        <v>544</v>
+      </c>
+      <c r="N18" s="1">
+        <v>571</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>102140</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>600</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>570</v>
+      </c>
+      <c r="C2" s="1">
+        <v>246</v>
+      </c>
+      <c r="D2" s="1">
+        <v>537</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>530</v>
+      </c>
+      <c r="C3" s="1">
+        <v>912</v>
+      </c>
+      <c r="D3" s="1">
+        <v>433</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>768</v>
+      </c>
+      <c r="C4" s="1">
+        <v>281</v>
+      </c>
+      <c r="D4" s="1">
+        <v>602</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1">
+        <v>155</v>
+      </c>
+      <c r="D7" s="1">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>176</v>
+      </c>
+      <c r="M7" s="1">
+        <v>431</v>
+      </c>
+      <c r="N7" s="1">
+        <v>540</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>64772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1">
+        <v>148</v>
+      </c>
+      <c r="D8" s="1">
+        <v>359</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>124</v>
+      </c>
+      <c r="M8" s="1">
+        <v>490</v>
+      </c>
+      <c r="N8" s="1">
+        <v>978</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>215903</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>213</v>
+      </c>
+      <c r="C9" s="1">
+        <v>94</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>173</v>
+      </c>
+      <c r="M9" s="1">
+        <v>460</v>
+      </c>
+      <c r="N9" s="1">
+        <v>733</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>41510</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>280</v>
+      </c>
+      <c r="C10" s="1">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1">
+        <v>261</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>277</v>
+      </c>
+      <c r="M10" s="1">
+        <v>537</v>
+      </c>
+      <c r="N10" s="1">
+        <v>563</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>122454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>224</v>
+      </c>
+      <c r="C11" s="1">
+        <v>191</v>
+      </c>
+      <c r="D11" s="1">
+        <v>170</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>246</v>
+      </c>
+      <c r="M11" s="1">
+        <v>555</v>
+      </c>
+      <c r="N11" s="1">
+        <v>510</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>123904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>356</v>
+      </c>
+      <c r="C12" s="1">
+        <v>204</v>
+      </c>
+      <c r="D12" s="1">
+        <v>174</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>157</v>
+      </c>
+      <c r="M12" s="1">
+        <v>345</v>
+      </c>
+      <c r="N12" s="1">
+        <v>790</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>131866</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>268</v>
+      </c>
+      <c r="C13" s="1">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1">
+        <v>323</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>18</v>
+      </c>
+      <c r="H13" s="1">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1">
+        <v>19</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>128</v>
+      </c>
+      <c r="M13" s="1">
+        <v>545</v>
+      </c>
+      <c r="N13" s="1">
+        <v>682</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>147732</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1">
+        <v>139</v>
+      </c>
+      <c r="D14" s="1">
+        <v>321</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>215</v>
+      </c>
+      <c r="M14" s="1">
+        <v>490</v>
+      </c>
+      <c r="N14" s="1">
+        <v>574</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>126612</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>132</v>
+      </c>
+      <c r="C15" s="1">
+        <v>219</v>
+      </c>
+      <c r="D15" s="1">
+        <v>268</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>259</v>
+      </c>
+      <c r="M15" s="1">
+        <v>412</v>
+      </c>
+      <c r="N15" s="1">
+        <v>504</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>129744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>251</v>
+      </c>
+      <c r="C16" s="1">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1">
+        <v>132</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1">
+        <v>15</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>122</v>
+      </c>
+      <c r="M16" s="1">
+        <v>334</v>
+      </c>
+      <c r="N16" s="1">
+        <v>918</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>80575</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1">
+        <v>295</v>
+      </c>
+      <c r="D17" s="1">
+        <v>42</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>140</v>
+      </c>
+      <c r="M17" s="1">
+        <v>373</v>
+      </c>
+      <c r="N17" s="1">
+        <v>511</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>67988</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>155</v>
+      </c>
+      <c r="C18" s="1">
+        <v>285</v>
+      </c>
+      <c r="D18" s="1">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>18</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>174</v>
+      </c>
+      <c r="M18" s="1">
+        <v>544</v>
+      </c>
+      <c r="N18" s="1">
+        <v>571</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>102140</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>800</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>570</v>
+      </c>
+      <c r="C2" s="1">
+        <v>246</v>
+      </c>
+      <c r="D2" s="1">
+        <v>537</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>530</v>
+      </c>
+      <c r="C3" s="1">
+        <v>912</v>
+      </c>
+      <c r="D3" s="1">
+        <v>433</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>768</v>
+      </c>
+      <c r="C4" s="1">
+        <v>281</v>
+      </c>
+      <c r="D4" s="1">
+        <v>602</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>65</v>
+      </c>
+      <c r="C7" s="1">
+        <v>155</v>
+      </c>
+      <c r="D7" s="1">
+        <v>95</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>176</v>
+      </c>
+      <c r="M7" s="1">
+        <v>431</v>
+      </c>
+      <c r="N7" s="1">
+        <v>540</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>64772</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>66</v>
+      </c>
+      <c r="C8" s="1">
+        <v>148</v>
+      </c>
+      <c r="D8" s="1">
+        <v>359</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2</v>
+      </c>
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>2</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>124</v>
+      </c>
+      <c r="M8" s="1">
+        <v>490</v>
+      </c>
+      <c r="N8" s="1">
+        <v>978</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>215903</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>213</v>
+      </c>
+      <c r="C9" s="1">
+        <v>94</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>19</v>
+      </c>
+      <c r="H9" s="1">
+        <v>11</v>
+      </c>
+      <c r="I9" s="1">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>173</v>
+      </c>
+      <c r="M9" s="1">
+        <v>460</v>
+      </c>
+      <c r="N9" s="1">
+        <v>733</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>41510</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>280</v>
+      </c>
+      <c r="C10" s="1">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1">
+        <v>261</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>10</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>277</v>
+      </c>
+      <c r="M10" s="1">
+        <v>537</v>
+      </c>
+      <c r="N10" s="1">
+        <v>563</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>122454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>224</v>
+      </c>
+      <c r="C11" s="1">
+        <v>191</v>
+      </c>
+      <c r="D11" s="1">
+        <v>170</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5</v>
+      </c>
+      <c r="H11" s="1">
+        <v>18</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>246</v>
+      </c>
+      <c r="M11" s="1">
+        <v>555</v>
+      </c>
+      <c r="N11" s="1">
+        <v>510</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>123904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>356</v>
+      </c>
+      <c r="C12" s="1">
+        <v>204</v>
+      </c>
+      <c r="D12" s="1">
+        <v>174</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1">
+        <v>19</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>157</v>
+      </c>
+      <c r="M12" s="1">
+        <v>345</v>
+      </c>
+      <c r="N12" s="1">
+        <v>790</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>131866</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>268</v>
+      </c>
+      <c r="C13" s="1">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1">
+        <v>323</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>18</v>
+      </c>
+      <c r="H13" s="1">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1">
+        <v>19</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>128</v>
+      </c>
+      <c r="M13" s="1">
+        <v>545</v>
+      </c>
+      <c r="N13" s="1">
+        <v>682</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>147732</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1">
+        <v>139</v>
+      </c>
+      <c r="D14" s="1">
+        <v>321</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>215</v>
+      </c>
+      <c r="M14" s="1">
+        <v>490</v>
+      </c>
+      <c r="N14" s="1">
+        <v>574</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>126612</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>132</v>
+      </c>
+      <c r="C15" s="1">
+        <v>219</v>
+      </c>
+      <c r="D15" s="1">
+        <v>268</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>19</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>259</v>
+      </c>
+      <c r="M15" s="1">
+        <v>412</v>
+      </c>
+      <c r="N15" s="1">
+        <v>504</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>129744</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>251</v>
+      </c>
+      <c r="C16" s="1">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1">
+        <v>132</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>10</v>
+      </c>
+      <c r="I16" s="1">
+        <v>15</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>122</v>
+      </c>
+      <c r="M16" s="1">
+        <v>334</v>
+      </c>
+      <c r="N16" s="1">
+        <v>918</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>80575</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1">
+        <v>295</v>
+      </c>
+      <c r="D17" s="1">
+        <v>42</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>140</v>
+      </c>
+      <c r="M17" s="1">
+        <v>373</v>
+      </c>
+      <c r="N17" s="1">
+        <v>511</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>67988</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>155</v>
+      </c>
+      <c r="C18" s="1">
+        <v>285</v>
+      </c>
+      <c r="D18" s="1">
+        <v>39</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1">
+        <v>18</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>174</v>
+      </c>
+      <c r="M18" s="1">
+        <v>544</v>
+      </c>
+      <c r="N18" s="1">
+        <v>571</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>102140</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>217</v>
+      </c>
+      <c r="C2" s="1">
+        <v>664</v>
+      </c>
+      <c r="D2" s="1">
+        <v>259</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>907</v>
+      </c>
+      <c r="C3" s="1">
+        <v>845</v>
+      </c>
+      <c r="D3" s="1">
+        <v>369</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>540</v>
+      </c>
+      <c r="C4" s="1">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1">
+        <v>120</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>134</v>
+      </c>
+      <c r="C7" s="1">
+        <v>223</v>
+      </c>
+      <c r="D7" s="1">
+        <v>226</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>20</v>
+      </c>
+      <c r="H7" s="1">
+        <v>4</v>
+      </c>
+      <c r="I7" s="1">
+        <v>16</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>294</v>
+      </c>
+      <c r="M7" s="1">
+        <v>336</v>
+      </c>
+      <c r="N7" s="1">
+        <v>998</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>169936</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>217</v>
+      </c>
+      <c r="C8" s="1">
+        <v>82</v>
+      </c>
+      <c r="D8" s="1">
+        <v>40</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>12</v>
+      </c>
+      <c r="H8" s="1">
+        <v>16</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>235</v>
+      </c>
+      <c r="M8" s="1">
+        <v>419</v>
+      </c>
+      <c r="N8" s="1">
+        <v>870</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>60076</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>53</v>
+      </c>
+      <c r="C9" s="1">
+        <v>115</v>
+      </c>
+      <c r="D9" s="1">
+        <v>242</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1">
+        <v>19</v>
+      </c>
+      <c r="I9" s="1">
+        <v>8</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>219</v>
+      </c>
+      <c r="M9" s="1">
+        <v>339</v>
+      </c>
+      <c r="N9" s="1">
+        <v>933</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>138189</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>180</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46</v>
+      </c>
+      <c r="D10" s="1">
+        <v>170</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>6</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1">
+        <v>7</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>123</v>
+      </c>
+      <c r="M10" s="1">
+        <v>599</v>
+      </c>
+      <c r="N10" s="1">
+        <v>859</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>97862</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>344</v>
+      </c>
+      <c r="C11" s="1">
+        <v>235</v>
+      </c>
+      <c r="D11" s="1">
+        <v>314</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>277</v>
+      </c>
+      <c r="M11" s="1">
+        <v>532</v>
+      </c>
+      <c r="N11" s="1">
+        <v>627</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>208593</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>313</v>
+      </c>
+      <c r="C12" s="1">
+        <v>361</v>
+      </c>
+      <c r="D12" s="1">
+        <v>211</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1">
+        <v>16</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>111</v>
+      </c>
+      <c r="M12" s="1">
+        <v>459</v>
+      </c>
+      <c r="N12" s="1">
+        <v>582</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>161622</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>339</v>
+      </c>
+      <c r="C13" s="1">
+        <v>83</v>
+      </c>
+      <c r="D13" s="1">
+        <v>275</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>5</v>
+      </c>
+      <c r="H13" s="1">
+        <v>19</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>120</v>
+      </c>
+      <c r="M13" s="1">
+        <v>529</v>
+      </c>
+      <c r="N13" s="1">
+        <v>725</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>141981</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>173</v>
+      </c>
+      <c r="C14" s="1">
+        <v>362</v>
+      </c>
+      <c r="D14" s="1">
+        <v>118</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>7</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1">
+        <v>16</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>213</v>
+      </c>
+      <c r="M14" s="1">
+        <v>540</v>
+      </c>
+      <c r="N14" s="1">
+        <v>587</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>150798</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>159</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
+        <v>236</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1">
+        <v>17</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>198</v>
+      </c>
+      <c r="M15" s="1">
+        <v>411</v>
+      </c>
+      <c r="N15" s="1">
+        <v>723</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>102082</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>61</v>
+      </c>
+      <c r="C16" s="1">
+        <v>77</v>
+      </c>
+      <c r="D16" s="1">
+        <v>97</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>6</v>
+      </c>
+      <c r="H16" s="1">
+        <v>8</v>
+      </c>
+      <c r="I16" s="1">
+        <v>7</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>208</v>
+      </c>
+      <c r="M16" s="1">
+        <v>365</v>
+      </c>
+      <c r="N16" s="1">
+        <v>778</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>58130</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>299</v>
+      </c>
+      <c r="C17" s="1">
+        <v>355</v>
+      </c>
+      <c r="D17" s="1">
+        <v>205</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>259</v>
+      </c>
+      <c r="M17" s="1">
+        <v>559</v>
+      </c>
+      <c r="N17" s="1">
+        <v>578</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>197188</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>353</v>
+      </c>
+      <c r="C18" s="1">
+        <v>240</v>
+      </c>
+      <c r="D18" s="1">
+        <v>349</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>6</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>16</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>214</v>
+      </c>
+      <c r="M18" s="1">
+        <v>501</v>
+      </c>
+      <c r="N18" s="1">
+        <v>982</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>269250</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
         <v>400</v>
       </c>
       <c r="B20" s="1"/>
@@ -4383,10 +9150,3163 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>781</v>
+      </c>
+      <c r="C2" s="1">
+        <v>743</v>
+      </c>
+      <c r="D2" s="1">
+        <v>119</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>987</v>
+      </c>
+      <c r="C3" s="1">
+        <v>849</v>
+      </c>
+      <c r="D3" s="1">
+        <v>747</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>907</v>
+      </c>
+      <c r="C4" s="1">
+        <v>777</v>
+      </c>
+      <c r="D4" s="1">
+        <v>892</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>190</v>
+      </c>
+      <c r="D7" s="1">
+        <v>310</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>17</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>175</v>
+      </c>
+      <c r="M7" s="1">
+        <v>540</v>
+      </c>
+      <c r="N7" s="1">
+        <v>971</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>204168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>109</v>
+      </c>
+      <c r="C8" s="1">
+        <v>337</v>
+      </c>
+      <c r="D8" s="1">
+        <v>114</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>167</v>
+      </c>
+      <c r="M8" s="1">
+        <v>542</v>
+      </c>
+      <c r="N8" s="1">
+        <v>860</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>149448</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>243</v>
+      </c>
+      <c r="C9" s="1">
+        <v>318</v>
+      </c>
+      <c r="D9" s="1">
+        <v>322</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1">
+        <v>18</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>209</v>
+      </c>
+      <c r="M9" s="1">
+        <v>448</v>
+      </c>
+      <c r="N9" s="1">
+        <v>732</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>214478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>297</v>
+      </c>
+      <c r="C10" s="1">
+        <v>226</v>
+      </c>
+      <c r="D10" s="1">
+        <v>167</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>11</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>235</v>
+      </c>
+      <c r="M10" s="1">
+        <v>491</v>
+      </c>
+      <c r="N10" s="1">
+        <v>737</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>151920</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>370</v>
+      </c>
+      <c r="C11" s="1">
+        <v>313</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>186</v>
+      </c>
+      <c r="M11" s="1">
+        <v>515</v>
+      </c>
+      <c r="N11" s="1">
+        <v>767</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>118842</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>94</v>
+      </c>
+      <c r="C12" s="1">
+        <v>228</v>
+      </c>
+      <c r="D12" s="1">
+        <v>41</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
+        <v>17</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>106</v>
+      </c>
+      <c r="M12" s="1">
+        <v>439</v>
+      </c>
+      <c r="N12" s="1">
+        <v>521</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>65708</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>274</v>
+      </c>
+      <c r="C13" s="1">
+        <v>358</v>
+      </c>
+      <c r="D13" s="1">
+        <v>183</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>131</v>
+      </c>
+      <c r="M13" s="1">
+        <v>389</v>
+      </c>
+      <c r="N13" s="1">
+        <v>631</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>145314</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>224</v>
+      </c>
+      <c r="C14" s="1">
+        <v>216</v>
+      </c>
+      <c r="D14" s="1">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>255</v>
+      </c>
+      <c r="M14" s="1">
+        <v>388</v>
+      </c>
+      <c r="N14" s="1">
+        <v>534</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>91023</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>372</v>
+      </c>
+      <c r="C15" s="1">
+        <v>268</v>
+      </c>
+      <c r="D15" s="1">
+        <v>224</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>139</v>
+      </c>
+      <c r="M15" s="1">
+        <v>308</v>
+      </c>
+      <c r="N15" s="1">
+        <v>609</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>135334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1">
+        <v>73</v>
+      </c>
+      <c r="D16" s="1">
+        <v>136</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1">
+        <v>7</v>
+      </c>
+      <c r="I16" s="1">
+        <v>16</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>298</v>
+      </c>
+      <c r="M16" s="1">
+        <v>588</v>
+      </c>
+      <c r="N16" s="1">
+        <v>585</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>73013</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>307</v>
+      </c>
+      <c r="C17" s="1">
+        <v>53</v>
+      </c>
+      <c r="D17" s="1">
+        <v>346</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>181</v>
+      </c>
+      <c r="M17" s="1">
+        <v>463</v>
+      </c>
+      <c r="N17" s="1">
+        <v>591</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>142296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>255</v>
+      </c>
+      <c r="C18" s="1">
+        <v>274</v>
+      </c>
+      <c r="D18" s="1">
+        <v>268</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>19</v>
+      </c>
+      <c r="H18" s="1">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>204</v>
+      </c>
+      <c r="M18" s="1">
+        <v>531</v>
+      </c>
+      <c r="N18" s="1">
+        <v>521</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>168571</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>200</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>781</v>
+      </c>
+      <c r="C2" s="1">
+        <v>743</v>
+      </c>
+      <c r="D2" s="1">
+        <v>119</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>987</v>
+      </c>
+      <c r="C3" s="1">
+        <v>849</v>
+      </c>
+      <c r="D3" s="1">
+        <v>747</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>907</v>
+      </c>
+      <c r="C4" s="1">
+        <v>777</v>
+      </c>
+      <c r="D4" s="1">
+        <v>892</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>190</v>
+      </c>
+      <c r="D7" s="1">
+        <v>310</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>17</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>175</v>
+      </c>
+      <c r="M7" s="1">
+        <v>540</v>
+      </c>
+      <c r="N7" s="1">
+        <v>971</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>204168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>109</v>
+      </c>
+      <c r="C8" s="1">
+        <v>337</v>
+      </c>
+      <c r="D8" s="1">
+        <v>114</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>167</v>
+      </c>
+      <c r="M8" s="1">
+        <v>542</v>
+      </c>
+      <c r="N8" s="1">
+        <v>860</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>149448</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>243</v>
+      </c>
+      <c r="C9" s="1">
+        <v>318</v>
+      </c>
+      <c r="D9" s="1">
+        <v>322</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1">
+        <v>18</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>209</v>
+      </c>
+      <c r="M9" s="1">
+        <v>448</v>
+      </c>
+      <c r="N9" s="1">
+        <v>732</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>214478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>297</v>
+      </c>
+      <c r="C10" s="1">
+        <v>226</v>
+      </c>
+      <c r="D10" s="1">
+        <v>167</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>11</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>235</v>
+      </c>
+      <c r="M10" s="1">
+        <v>491</v>
+      </c>
+      <c r="N10" s="1">
+        <v>737</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>151920</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>370</v>
+      </c>
+      <c r="C11" s="1">
+        <v>313</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>186</v>
+      </c>
+      <c r="M11" s="1">
+        <v>515</v>
+      </c>
+      <c r="N11" s="1">
+        <v>767</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>118842</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>94</v>
+      </c>
+      <c r="C12" s="1">
+        <v>228</v>
+      </c>
+      <c r="D12" s="1">
+        <v>41</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
+        <v>17</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>106</v>
+      </c>
+      <c r="M12" s="1">
+        <v>439</v>
+      </c>
+      <c r="N12" s="1">
+        <v>521</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>65708</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>274</v>
+      </c>
+      <c r="C13" s="1">
+        <v>358</v>
+      </c>
+      <c r="D13" s="1">
+        <v>183</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>131</v>
+      </c>
+      <c r="M13" s="1">
+        <v>389</v>
+      </c>
+      <c r="N13" s="1">
+        <v>631</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>145314</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>224</v>
+      </c>
+      <c r="C14" s="1">
+        <v>216</v>
+      </c>
+      <c r="D14" s="1">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>255</v>
+      </c>
+      <c r="M14" s="1">
+        <v>388</v>
+      </c>
+      <c r="N14" s="1">
+        <v>534</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>91023</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>372</v>
+      </c>
+      <c r="C15" s="1">
+        <v>268</v>
+      </c>
+      <c r="D15" s="1">
+        <v>224</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>139</v>
+      </c>
+      <c r="M15" s="1">
+        <v>308</v>
+      </c>
+      <c r="N15" s="1">
+        <v>609</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>135334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1">
+        <v>73</v>
+      </c>
+      <c r="D16" s="1">
+        <v>136</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1">
+        <v>7</v>
+      </c>
+      <c r="I16" s="1">
+        <v>16</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>298</v>
+      </c>
+      <c r="M16" s="1">
+        <v>588</v>
+      </c>
+      <c r="N16" s="1">
+        <v>585</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>73013</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>307</v>
+      </c>
+      <c r="C17" s="1">
+        <v>53</v>
+      </c>
+      <c r="D17" s="1">
+        <v>346</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>181</v>
+      </c>
+      <c r="M17" s="1">
+        <v>463</v>
+      </c>
+      <c r="N17" s="1">
+        <v>591</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>142296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>255</v>
+      </c>
+      <c r="C18" s="1">
+        <v>274</v>
+      </c>
+      <c r="D18" s="1">
+        <v>268</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>19</v>
+      </c>
+      <c r="H18" s="1">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>204</v>
+      </c>
+      <c r="M18" s="1">
+        <v>531</v>
+      </c>
+      <c r="N18" s="1">
+        <v>521</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>168571</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>400</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>781</v>
+      </c>
+      <c r="C2" s="1">
+        <v>743</v>
+      </c>
+      <c r="D2" s="1">
+        <v>119</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>987</v>
+      </c>
+      <c r="C3" s="1">
+        <v>849</v>
+      </c>
+      <c r="D3" s="1">
+        <v>747</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>907</v>
+      </c>
+      <c r="C4" s="1">
+        <v>777</v>
+      </c>
+      <c r="D4" s="1">
+        <v>892</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>190</v>
+      </c>
+      <c r="D7" s="1">
+        <v>310</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>17</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>175</v>
+      </c>
+      <c r="M7" s="1">
+        <v>540</v>
+      </c>
+      <c r="N7" s="1">
+        <v>971</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>204168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>109</v>
+      </c>
+      <c r="C8" s="1">
+        <v>337</v>
+      </c>
+      <c r="D8" s="1">
+        <v>114</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>167</v>
+      </c>
+      <c r="M8" s="1">
+        <v>542</v>
+      </c>
+      <c r="N8" s="1">
+        <v>860</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>149448</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>243</v>
+      </c>
+      <c r="C9" s="1">
+        <v>318</v>
+      </c>
+      <c r="D9" s="1">
+        <v>322</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1">
+        <v>18</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>209</v>
+      </c>
+      <c r="M9" s="1">
+        <v>448</v>
+      </c>
+      <c r="N9" s="1">
+        <v>732</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>214478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>297</v>
+      </c>
+      <c r="C10" s="1">
+        <v>226</v>
+      </c>
+      <c r="D10" s="1">
+        <v>167</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>11</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>235</v>
+      </c>
+      <c r="M10" s="1">
+        <v>491</v>
+      </c>
+      <c r="N10" s="1">
+        <v>737</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>151920</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>370</v>
+      </c>
+      <c r="C11" s="1">
+        <v>313</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>186</v>
+      </c>
+      <c r="M11" s="1">
+        <v>515</v>
+      </c>
+      <c r="N11" s="1">
+        <v>767</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>118842</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>94</v>
+      </c>
+      <c r="C12" s="1">
+        <v>228</v>
+      </c>
+      <c r="D12" s="1">
+        <v>41</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
+        <v>17</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>106</v>
+      </c>
+      <c r="M12" s="1">
+        <v>439</v>
+      </c>
+      <c r="N12" s="1">
+        <v>521</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>65708</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>274</v>
+      </c>
+      <c r="C13" s="1">
+        <v>358</v>
+      </c>
+      <c r="D13" s="1">
+        <v>183</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>131</v>
+      </c>
+      <c r="M13" s="1">
+        <v>389</v>
+      </c>
+      <c r="N13" s="1">
+        <v>631</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>145314</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>224</v>
+      </c>
+      <c r="C14" s="1">
+        <v>216</v>
+      </c>
+      <c r="D14" s="1">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>255</v>
+      </c>
+      <c r="M14" s="1">
+        <v>388</v>
+      </c>
+      <c r="N14" s="1">
+        <v>534</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>91023</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>372</v>
+      </c>
+      <c r="C15" s="1">
+        <v>268</v>
+      </c>
+      <c r="D15" s="1">
+        <v>224</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>139</v>
+      </c>
+      <c r="M15" s="1">
+        <v>308</v>
+      </c>
+      <c r="N15" s="1">
+        <v>609</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>135334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1">
+        <v>73</v>
+      </c>
+      <c r="D16" s="1">
+        <v>136</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1">
+        <v>7</v>
+      </c>
+      <c r="I16" s="1">
+        <v>16</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>298</v>
+      </c>
+      <c r="M16" s="1">
+        <v>588</v>
+      </c>
+      <c r="N16" s="1">
+        <v>585</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>73013</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>307</v>
+      </c>
+      <c r="C17" s="1">
+        <v>53</v>
+      </c>
+      <c r="D17" s="1">
+        <v>346</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>181</v>
+      </c>
+      <c r="M17" s="1">
+        <v>463</v>
+      </c>
+      <c r="N17" s="1">
+        <v>591</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>142296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>255</v>
+      </c>
+      <c r="C18" s="1">
+        <v>274</v>
+      </c>
+      <c r="D18" s="1">
+        <v>268</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>19</v>
+      </c>
+      <c r="H18" s="1">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>204</v>
+      </c>
+      <c r="M18" s="1">
+        <v>531</v>
+      </c>
+      <c r="N18" s="1">
+        <v>521</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>168571</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>600</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col customWidth="1" min="1" max="17" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>781</v>
+      </c>
+      <c r="C2" s="1">
+        <v>743</v>
+      </c>
+      <c r="D2" s="1">
+        <v>119</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>987</v>
+      </c>
+      <c r="C3" s="1">
+        <v>849</v>
+      </c>
+      <c r="D3" s="1">
+        <v>747</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>907</v>
+      </c>
+      <c r="C4" s="1">
+        <v>777</v>
+      </c>
+      <c r="D4" s="1">
+        <v>892</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>3</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>3</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>190</v>
+      </c>
+      <c r="D7" s="1">
+        <v>310</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>17</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
+        <v>175</v>
+      </c>
+      <c r="M7" s="1">
+        <v>540</v>
+      </c>
+      <c r="N7" s="1">
+        <v>971</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>204168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1">
+        <v>109</v>
+      </c>
+      <c r="C8" s="1">
+        <v>337</v>
+      </c>
+      <c r="D8" s="1">
+        <v>114</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="L8" s="1">
+        <v>167</v>
+      </c>
+      <c r="M8" s="1">
+        <v>542</v>
+      </c>
+      <c r="N8" s="1">
+        <v>860</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>149448</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1">
+        <v>243</v>
+      </c>
+      <c r="C9" s="1">
+        <v>318</v>
+      </c>
+      <c r="D9" s="1">
+        <v>322</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="1">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1">
+        <v>18</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
+        <v>209</v>
+      </c>
+      <c r="M9" s="1">
+        <v>448</v>
+      </c>
+      <c r="N9" s="1">
+        <v>732</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>214478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>297</v>
+      </c>
+      <c r="C10" s="1">
+        <v>226</v>
+      </c>
+      <c r="D10" s="1">
+        <v>167</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>18</v>
+      </c>
+      <c r="I10" s="1">
+        <v>11</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1">
+        <v>4</v>
+      </c>
+      <c r="L10" s="1">
+        <v>235</v>
+      </c>
+      <c r="M10" s="1">
+        <v>491</v>
+      </c>
+      <c r="N10" s="1">
+        <v>737</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>151920</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1">
+        <v>370</v>
+      </c>
+      <c r="C11" s="1">
+        <v>313</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>20</v>
+      </c>
+      <c r="I11" s="1">
+        <v>13</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>5</v>
+      </c>
+      <c r="L11" s="1">
+        <v>186</v>
+      </c>
+      <c r="M11" s="1">
+        <v>515</v>
+      </c>
+      <c r="N11" s="1">
+        <v>767</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>118842</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1">
+        <v>94</v>
+      </c>
+      <c r="C12" s="1">
+        <v>228</v>
+      </c>
+      <c r="D12" s="1">
+        <v>41</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>10</v>
+      </c>
+      <c r="I12" s="1">
+        <v>17</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
+        <v>106</v>
+      </c>
+      <c r="M12" s="1">
+        <v>439</v>
+      </c>
+      <c r="N12" s="1">
+        <v>521</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>65708</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1">
+        <v>274</v>
+      </c>
+      <c r="C13" s="1">
+        <v>358</v>
+      </c>
+      <c r="D13" s="1">
+        <v>183</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <v>7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>2</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1">
+        <v>7</v>
+      </c>
+      <c r="L13" s="1">
+        <v>131</v>
+      </c>
+      <c r="M13" s="1">
+        <v>389</v>
+      </c>
+      <c r="N13" s="1">
+        <v>631</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>145314</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>224</v>
+      </c>
+      <c r="C14" s="1">
+        <v>216</v>
+      </c>
+      <c r="D14" s="1">
+        <v>77</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1">
+        <v>12</v>
+      </c>
+      <c r="H14" s="1">
+        <v>12</v>
+      </c>
+      <c r="I14" s="1">
+        <v>15</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>8</v>
+      </c>
+      <c r="L14" s="1">
+        <v>255</v>
+      </c>
+      <c r="M14" s="1">
+        <v>388</v>
+      </c>
+      <c r="N14" s="1">
+        <v>534</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>91023</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>372</v>
+      </c>
+      <c r="C15" s="1">
+        <v>268</v>
+      </c>
+      <c r="D15" s="1">
+        <v>224</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>139</v>
+      </c>
+      <c r="M15" s="1">
+        <v>308</v>
+      </c>
+      <c r="N15" s="1">
+        <v>609</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>135334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1">
+        <v>73</v>
+      </c>
+      <c r="D16" s="1">
+        <v>136</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
+        <v>10</v>
+      </c>
+      <c r="G16" s="1">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1">
+        <v>7</v>
+      </c>
+      <c r="I16" s="1">
+        <v>16</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1">
+        <v>10</v>
+      </c>
+      <c r="L16" s="1">
+        <v>298</v>
+      </c>
+      <c r="M16" s="1">
+        <v>588</v>
+      </c>
+      <c r="N16" s="1">
+        <v>585</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>73013</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>307</v>
+      </c>
+      <c r="C17" s="1">
+        <v>53</v>
+      </c>
+      <c r="D17" s="1">
+        <v>346</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>18</v>
+      </c>
+      <c r="I17" s="1">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
+        <v>11</v>
+      </c>
+      <c r="L17" s="1">
+        <v>181</v>
+      </c>
+      <c r="M17" s="1">
+        <v>463</v>
+      </c>
+      <c r="N17" s="1">
+        <v>591</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>142296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>12</v>
+      </c>
+      <c r="B18" s="1">
+        <v>255</v>
+      </c>
+      <c r="C18" s="1">
+        <v>274</v>
+      </c>
+      <c r="D18" s="1">
+        <v>268</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1">
+        <v>19</v>
+      </c>
+      <c r="H18" s="1">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>8</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1">
+        <v>12</v>
+      </c>
+      <c r="L18" s="1">
+        <v>204</v>
+      </c>
+      <c r="M18" s="1">
+        <v>531</v>
+      </c>
+      <c r="N18" s="1">
+        <v>521</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>168571</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>800</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
